--- a/data/research-experience_eng_S.xlsx
+++ b/data/research-experience_eng_S.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27531"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27928"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21FEE1FB-D5B3-44E3-B823-73CE03320AB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63C5E30E-1F37-4B05-988D-B4596CBAC943}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -49,9 +49,6 @@
     <t>Visiting Professor</t>
   </si>
   <si>
-    <t>Dec.2023 - Present</t>
-  </si>
-  <si>
     <t>\href{https://www.cuc.edu.co/}{Universidad de la Costa}</t>
   </si>
   <si>
@@ -71,6 +68,9 @@
   </si>
   <si>
     <t>why</t>
+  </si>
+  <si>
+    <t>Dec.2023 - Dec. 2024</t>
   </si>
 </sst>
 </file>
@@ -395,15 +395,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:E4"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="18.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="18.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="28.28515625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="52.28515625" customWidth="1"/>
+    <col min="1" max="1" width="18.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.44140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="28.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="52.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -417,10 +417,10 @@
         <v>3</v>
       </c>
       <c r="E1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="45" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>4</v>
       </c>
@@ -434,32 +434,32 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>8</v>
       </c>
       <c r="B3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="D3" t="s">
         <v>10</v>
       </c>
-      <c r="D3" t="s">
+    </row>
+    <row r="4" spans="1:5" ht="72" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="4" spans="1:5" ht="90" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
+      <c r="B4" t="s">
         <v>12</v>
       </c>
-      <c r="B4" t="s">
+      <c r="C4" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D4" t="s">
         <v>13</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="D4" t="s">
-        <v>14</v>
       </c>
     </row>
   </sheetData>
